--- a/src/main/resources/templates/excel/formatoSeccionesConCruce.xlsx
+++ b/src/main/resources/templates/excel/formatoSeccionesConCruce.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21901"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96BAC7FD-80E1-4723-A78C-E9B9D1128AF5}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BC79A3E-A208-4BD0-BC24-AC959011100C}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,15 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>UNIVERSIDAD NACIONAL AGRARIA LA MOLINA</t>
   </si>
   <si>
     <t>CENTRO MÉDICO</t>
-  </si>
-  <si>
-    <t>CICLO ACADEMICO 2018-II</t>
   </si>
   <si>
     <t>SECCIÓN</t>
@@ -585,7 +582,7 @@
     </row>
     <row r="3" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B3" s="11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3" s="11"/>
       <c r="D3" s="11"/>
@@ -605,9 +602,7 @@
       <c r="R3" s="1"/>
     </row>
     <row r="4" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B4" s="12" t="s">
-        <v>2</v>
-      </c>
+      <c r="B4" s="12"/>
       <c r="C4" s="12"/>
       <c r="D4" s="12"/>
       <c r="E4" s="12"/>
@@ -636,31 +631,31 @@
     <row r="6" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="7" spans="1:18" ht="34.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>12</v>
-      </c>
       <c r="C7" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="D7" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="9" t="s">
+      <c r="G7" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="H7" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="I7" s="9" t="s">
         <v>6</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/templates/excel/formatoSeccionesConCruce.xlsx
+++ b/src/main/resources/templates/excel/formatoSeccionesConCruce.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21901"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BC79A3E-A208-4BD0-BC24-AC959011100C}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{850F0D0A-DC5A-43C4-A61D-BD595928293C}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>UNIVERSIDAD NACIONAL AGRARIA LA MOLINA</t>
   </si>
@@ -56,6 +56,12 @@
   </si>
   <si>
     <t>NOMBRE CURSO</t>
+  </si>
+  <si>
+    <t>VACANTES</t>
+  </si>
+  <si>
+    <t>MATRICULADOS</t>
   </si>
 </sst>
 </file>
@@ -525,20 +531,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R7"/>
+  <dimension ref="A1:T7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.33203125" customWidth="1"/>
     <col min="2" max="2" width="31.109375" customWidth="1"/>
-    <col min="3" max="3" width="15.21875" customWidth="1"/>
-    <col min="4" max="4" width="18.44140625" customWidth="1"/>
-    <col min="5" max="5" width="40" customWidth="1"/>
-    <col min="6" max="6" width="13.44140625" customWidth="1"/>
-    <col min="7" max="7" width="20.33203125" customWidth="1"/>
-    <col min="8" max="9" width="26.33203125" customWidth="1"/>
+    <col min="3" max="4" width="15.21875" customWidth="1"/>
+    <col min="5" max="5" width="18.5546875" customWidth="1"/>
+    <col min="6" max="6" width="18.44140625" customWidth="1"/>
+    <col min="7" max="7" width="40" customWidth="1"/>
+    <col min="8" max="8" width="13.44140625" customWidth="1"/>
+    <col min="9" max="9" width="20.33203125" customWidth="1"/>
+    <col min="10" max="11" width="26.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="10" t="s">
         <v>0</v>
       </c>
@@ -547,8 +554,8 @@
       <c r="E1" s="10"/>
       <c r="F1" s="10"/>
       <c r="G1" s="10"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
@@ -556,10 +563,12 @@
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
     </row>
-    <row r="2" spans="1:18" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="11" t="s">
         <v>1</v>
       </c>
@@ -568,8 +577,8 @@
       <c r="E2" s="11"/>
       <c r="F2" s="11"/>
       <c r="G2" s="11"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
@@ -577,10 +586,12 @@
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
-      <c r="Q2" s="1"/>
-      <c r="R2" s="1"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
     </row>
-    <row r="3" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B3" s="11" t="s">
         <v>7</v>
       </c>
@@ -589,8 +600,8 @@
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="11"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
@@ -598,18 +609,20 @@
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
       <c r="P3" s="3"/>
-      <c r="Q3" s="1"/>
-      <c r="R3" s="1"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
+      <c r="S3" s="1"/>
+      <c r="T3" s="1"/>
     </row>
-    <row r="4" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B4" s="12"/>
       <c r="C4" s="12"/>
       <c r="D4" s="12"/>
       <c r="E4" s="12"/>
       <c r="F4" s="12"/>
       <c r="G4" s="12"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
       <c r="J4" s="4"/>
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
@@ -617,19 +630,23 @@
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
-      <c r="Q4" s="1"/>
-      <c r="R4" s="1"/>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="4"/>
+      <c r="S4" s="1"/>
+      <c r="T4" s="1"/>
     </row>
-    <row r="5" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
     </row>
-    <row r="6" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="7" spans="1:18" ht="34.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="7" spans="1:20" ht="34.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
         <v>10</v>
       </c>
@@ -640,30 +657,36 @@
         <v>2</v>
       </c>
       <c r="D7" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="G7" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="H7" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="I7" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="J7" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="I7" s="9" t="s">
+      <c r="K7" s="9" t="s">
         <v>6</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="B4:I4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="124" orientation="portrait" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>
